--- a/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T15:29:00+00:00</t>
+    <t>2025-03-12T13:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2149" uniqueCount="401">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T13:18:22+00:00</t>
+    <t>2025-03-14T15:47:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/RelatedPerson</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -314,13 +314,203 @@
 </t>
   </si>
   <si>
-    <t>RelatedPerson.implicitRules</t>
+    <t>RelatedPerson.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>RelatedPerson.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>RelatedPerson.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>RelatedPerson.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>RelatedPerson.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>RelatedPerson.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
+</t>
+  </si>
+  <si>
+    <t>Slice based on the canonical url value</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>RelatedPerson.meta.profile:fr-canonical</t>
+  </si>
+  <si>
+    <t>fr-canonical</t>
+  </si>
+  <si>
+    <t>RelatedPerson.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>RelatedPerson.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>RelatedPerson.implicitRules</t>
+  </si>
+  <si>
     <t>A set of rules under which this content was created</t>
   </si>
   <si>
@@ -416,28 +606,10 @@
     <t>RelatedPerson.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>RelatedPerson.modifierExtension</t>
@@ -512,7 +684,7 @@
     <t>RelatedPerson.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
 </t>
   </si>
   <si>
@@ -538,28 +710,305 @@
 </t>
   </si>
   <si>
+    <t>The nature of the relationship</t>
+  </si>
+  <si>
+    <t>The nature of the relationship between a patient and the related person.</t>
+  </si>
+  <si>
+    <t>We need to know the relationship with the patient since it influences the interpretation of the information attributed to this person.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/relatedperson-relationshiptype</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:coding.system}
+</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>NK1-3</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:Role</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>The nature of the relationship. Rôle de la personne. Ex : personne de confiance, aidant ...</t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-contact-role</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:Role.id</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship.id</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:Role.extension</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship.extension</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:Role.coding</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship.coding</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:Role.coding.id</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship.coding.id</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:Role.coding.extension</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship.coding.extension</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:Role.coding.system</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R260-HL7RoleClass/FHIR/TRE-R260-HL7RoleClass</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:Role.coding.version</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:Role.coding.code</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>CON</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:Role.coding.display</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Informateur</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:Role.coding.userSelected</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship.coding.userSelected</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:Role.text</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:RelationType</t>
+  </si>
+  <si>
+    <t>RelationType</t>
+  </si>
+  <si>
     <t>Lien de la personne avec le patient/usager</t>
   </si>
   <si>
-    <t>The nature of the relationship between a patient and the related person.</t>
-  </si>
-  <si>
-    <t>We need to know the relationship with the patient since it influences the interpretation of the information attributed to this person.</t>
-  </si>
-  <si>
     <t>required</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J11-RelationPatient-CISIS/FHIR/JDV-J11-RelationPatient-CISIS</t>
   </si>
   <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>NK1-3</t>
+    <t>RelatedPerson.relationship:RelationType.id</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:RelationType.extension</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:RelationType.coding</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:RelationType.coding.id</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:RelationType.coding.extension</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:RelationType.coding.system</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R216-HL7RoleCode/FHIR/TRE-R216-HL7RoleCode</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:RelationType.coding.version</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:RelationType.coding.code</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:RelationType.coding.display</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:RelationType.coding.userSelected</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:RelationType.text</t>
   </si>
   <si>
     <t>RelatedPerson.name</t>
@@ -572,29 +1021,36 @@
     <t>Nom de la personne</t>
   </si>
   <si>
-    <t>A name associated with the person.</t>
+    <t>A human's name with the ability to identify parts and usage.</t>
+  </si>
+  <si>
+    <t>Names may be changed, or repudiated, or people may have different names in different contexts. Names may be divided into parts of different type that have variable significance depending on context, though the division into parts does not always matter. With personal names, the different parts might or might not be imbued with some implicit meaning; various cultures associate different importance with the name parts and the degree to which systems must care about name parts around the world varies widely.</t>
   </si>
   <si>
     <t>Related persons need to be identified by name, but it is uncommon to need details about multiple other names for that person.</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>NK1-2</t>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>EN (actually, PN)</t>
+  </si>
+  <si>
+    <t>XPN</t>
   </si>
   <si>
     <t>RelatedPerson.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point}
 </t>
   </si>
   <si>
-    <t>Coordonnées télécom</t>
-  </si>
-  <si>
-    <t>A contact detail for the person, e.g. a telephone number or an email address.</t>
+    <t>Details of a Technology mediated contact point (phone, fax, email, etc.)</t>
+  </si>
+  <si>
+    <t>Details for all kinds of technology mediated contact points for a person or organization, including telephone, email, etc.</t>
   </si>
   <si>
     <t>Person may have multiple ways to be contacted with different uses or applicable periods.  May need to have options for contacting the person urgently, and also to help with identification.</t>
@@ -603,10 +1059,14 @@
     <t>People have (primary) ways to contact them in some way such as phone, email.</t>
   </si>
   <si>
-    <t>telecom</t>
-  </si>
-  <si>
-    <t>NK1-5 / NK1-6 / NK1-40</t>
+    <t>cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
+  </si>
+  <si>
+    <t>TEL</t>
+  </si>
+  <si>
+    <t>XTN</t>
   </si>
   <si>
     <t>RelatedPerson.gender</t>
@@ -652,23 +1112,26 @@
     <t>RelatedPerson.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address
+    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address}
 </t>
   </si>
   <si>
-    <t>Adresse</t>
-  </si>
-  <si>
-    <t>Address where the related person can be contacted or visited.</t>
+    <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats)</t>
+  </si>
+  <si>
+    <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats).  This data type may be used to convey addresses for use in delivering mail as well as for visiting locations which might not be valid for mail delivery.  There are a variety of postal address formats defined around the world.</t>
+  </si>
+  <si>
+    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](http://hl7.org/fhir/R4/location.html#) resource).</t>
   </si>
   <si>
     <t>Need to keep track where the related person can be contacted per postal mail or visited.</t>
   </si>
   <si>
-    <t>addr</t>
-  </si>
-  <si>
-    <t>NK1-4</t>
+    <t>AD</t>
+  </si>
+  <si>
+    <t>XAD</t>
   </si>
   <si>
     <t>RelatedPerson.photo</t>
@@ -737,29 +1200,7 @@
     <t>RelatedPerson.communication.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>RelatedPerson.communication.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>RelatedPerson.communication.modifierExtension</t>
@@ -1114,12 +1555,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM27"/>
+  <dimension ref="A1:AM60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="46.27734375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="57.6171875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="46.27734375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="13.0859375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1141,11 +1582,11 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="53.953125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="89.85546875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="38.27734375" customWidth="true" bestFit="true" hidden="true"/>
@@ -1154,7 +1595,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="89.0078125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="28.1484375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="45.6171875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1627,10 +2068,10 @@
         <v>76</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>99</v>
@@ -1641,9 +2082,7 @@
       <c r="M5" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="N5" t="s" s="2">
-        <v>102</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>76</v>
@@ -1692,7 +2131,7 @@
         <v>76</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>77</v>
@@ -1704,10 +2143,10 @@
         <v>76</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>76</v>
@@ -1725,14 +2164,14 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>76</v>
@@ -1744,16 +2183,16 @@
         <v>76</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -1779,46 +2218,46 @@
         <v>76</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="Y6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB6" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AC6" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>76</v>
-      </c>
       <c r="AD6" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="AL6" t="s" s="2">
         <v>76</v>
@@ -1829,14 +2268,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -1852,10 +2291,10 @@
         <v>76</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>116</v>
@@ -1929,7 +2368,7 @@
         <v>97</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>76</v>
@@ -1940,21 +2379,21 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>122</v>
+        <v>76</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>76</v>
@@ -1963,19 +2402,19 @@
         <v>76</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="M8" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>124</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>126</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2025,22 +2464,22 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>76</v>
@@ -2051,21 +2490,21 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>76</v>
@@ -2074,19 +2513,19 @@
         <v>76</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2136,22 +2575,22 @@
         <v>76</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>76</v>
@@ -2162,14 +2601,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2182,26 +2621,24 @@
         <v>76</v>
       </c>
       <c r="I10" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J10" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="J10" t="s" s="2">
-        <v>76</v>
-      </c>
       <c r="K10" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>76</v>
       </c>
@@ -2237,19 +2674,19 @@
         <v>76</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2261,10 +2698,10 @@
         <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>76</v>
@@ -2275,12 +2712,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="D11" t="s" s="2">
         <v>76</v>
       </c>
@@ -2289,7 +2728,7 @@
         <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>76</v>
@@ -2301,18 +2740,18 @@
         <v>86</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N11" s="2"/>
-      <c r="O11" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>76</v>
       </c>
@@ -2321,7 +2760,7 @@
         <v>76</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>76</v>
@@ -2360,7 +2799,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -2375,21 +2814,21 @@
         <v>97</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>147</v>
+        <v>76</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>148</v>
+        <v>76</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>149</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2400,38 +2839,34 @@
         <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="Q12" t="s" s="2">
-        <v>156</v>
-      </c>
+      <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
         <v>76</v>
       </c>
@@ -2451,13 +2886,13 @@
         <v>76</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>76</v>
+        <v>147</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>76</v>
+        <v>148</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>76</v>
+        <v>149</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>76</v>
@@ -2481,7 +2916,7 @@
         <v>77</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>76</v>
@@ -2490,10 +2925,10 @@
         <v>97</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>157</v>
+        <v>76</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>158</v>
+        <v>76</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>76</v>
@@ -2501,10 +2936,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2512,10 +2947,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>76</v>
@@ -2527,18 +2962,18 @@
         <v>86</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N13" s="2"/>
-      <c r="O13" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>76</v>
       </c>
@@ -2562,13 +2997,13 @@
         <v>76</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>76</v>
+        <v>155</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>76</v>
+        <v>156</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>76</v>
+        <v>157</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>76</v>
@@ -2586,13 +3021,13 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>76</v>
@@ -2601,21 +3036,21 @@
         <v>97</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>164</v>
+        <v>76</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>165</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2632,24 +3067,24 @@
         <v>76</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>167</v>
+        <v>127</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N14" s="2"/>
-      <c r="O14" t="s" s="2">
-        <v>170</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>76</v>
       </c>
@@ -2673,11 +3108,13 @@
         <v>76</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="Y14" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="Z14" t="s" s="2">
-        <v>172</v>
+        <v>76</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>76</v>
@@ -2695,13 +3132,13 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>76</v>
@@ -2710,21 +3147,21 @@
         <v>97</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>173</v>
+        <v>76</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>174</v>
+        <v>76</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>175</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2732,7 +3169,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>85</v>
@@ -2744,21 +3181,21 @@
         <v>76</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N15" s="2"/>
-      <c r="O15" t="s" s="2">
-        <v>180</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>76</v>
       </c>
@@ -2782,13 +3219,13 @@
         <v>76</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>76</v>
+        <v>169</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>76</v>
+        <v>170</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>76</v>
+        <v>171</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>76</v>
@@ -2806,13 +3243,13 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>76</v>
@@ -2821,32 +3258,32 @@
         <v>97</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>181</v>
+        <v>76</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>182</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>76</v>
+        <v>174</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>76</v>
@@ -2855,23 +3292,21 @@
         <v>76</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>76</v>
       </c>
@@ -2919,13 +3354,13 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>76</v>
@@ -2934,32 +3369,32 @@
         <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>190</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>76</v>
+        <v>182</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>76</v>
@@ -2968,21 +3403,21 @@
         <v>76</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>105</v>
+        <v>183</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>76</v>
       </c>
@@ -3006,13 +3441,13 @@
         <v>76</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>171</v>
+        <v>76</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>195</v>
+        <v>76</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>196</v>
+        <v>76</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>76</v>
@@ -3030,47 +3465,47 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>198</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>76</v>
@@ -3079,18 +3514,20 @@
         <v>76</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>200</v>
+        <v>106</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>201</v>
+        <v>107</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>109</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>76</v>
@@ -3139,22 +3576,22 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>76</v>
@@ -3165,14 +3602,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3185,23 +3622,25 @@
         <v>76</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>205</v>
+        <v>106</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>109</v>
+      </c>
       <c r="O19" t="s" s="2">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>76</v>
@@ -3250,7 +3689,7 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3262,24 +3701,24 @@
         <v>76</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>209</v>
+        <v>188</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>210</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3287,10 +3726,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>76</v>
@@ -3299,20 +3738,20 @@
         <v>76</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>76</v>
@@ -3361,7 +3800,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3376,21 +3815,21 @@
         <v>97</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>76</v>
+        <v>203</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>217</v>
+        <v>204</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3407,26 +3846,32 @@
         <v>76</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="Q21" s="2"/>
+      <c r="Q21" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="R21" t="s" s="2">
         <v>76</v>
       </c>
@@ -3470,7 +3915,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3485,10 +3930,10 @@
         <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>76</v>
@@ -3496,10 +3941,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3507,10 +3952,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>76</v>
@@ -3519,22 +3964,20 @@
         <v>76</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>76</v>
@@ -3583,13 +4026,13 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>76</v>
@@ -3598,21 +4041,21 @@
         <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>76</v>
+        <v>220</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3623,7 +4066,7 @@
         <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>76</v>
@@ -3632,19 +4075,21 @@
         <v>76</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+      <c r="O23" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>76</v>
       </c>
@@ -3668,71 +4113,71 @@
         <v>76</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>76</v>
+        <v>169</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>76</v>
+        <v>224</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>76</v>
+        <v>226</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>76</v>
+        <v>229</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>76</v>
+        <v>230</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="D24" t="s" s="2">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>76</v>
@@ -3741,21 +4186,21 @@
         <v>76</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>131</v>
+        <v>222</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>132</v>
+        <v>233</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>76</v>
       </c>
@@ -3779,13 +4224,11 @@
         <v>76</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>76</v>
+        <v>234</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>76</v>
@@ -3803,7 +4246,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -3815,60 +4258,56 @@
         <v>76</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>76</v>
+        <v>229</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>76</v>
+        <v>230</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>241</v>
+        <v>76</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>242</v>
+        <v>100</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>76</v>
       </c>
@@ -3916,22 +4355,22 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>244</v>
+        <v>102</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>76</v>
@@ -3942,21 +4381,21 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>76</v>
@@ -3968,20 +4407,18 @@
         <v>76</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>167</v>
+        <v>106</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>246</v>
+        <v>107</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>247</v>
+        <v>108</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>76</v>
       </c>
@@ -4005,46 +4442,46 @@
         <v>76</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB26" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="Z26" t="s" s="2">
+      <c r="AC26" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="AA26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>76</v>
-      </c>
       <c r="AD26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>245</v>
+        <v>113</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>250</v>
+        <v>103</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>76</v>
@@ -4055,10 +4492,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4069,7 +4506,7 @@
         <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>76</v>
@@ -4078,22 +4515,22 @@
         <v>76</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>76</v>
@@ -4142,13 +4579,13 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>76</v>
@@ -4157,12 +4594,3691 @@
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="O29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AL27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM27" t="s" s="2">
+      <c r="O30" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="P30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O31" s="2"/>
+      <c r="P31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="P32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="P33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="P34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="P35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="D36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="P36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="Y36" s="2"/>
+      <c r="Z36" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="P39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="P42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O43" s="2"/>
+      <c r="P43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="P44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="P45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="P46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="P47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="P48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="P49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="P50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="P52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="P53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="P55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="P60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>76</v>
       </c>
     </row>

--- a/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-14T15:47:10+00:00</t>
+    <t>2025-03-25T13:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T13:52:25+00:00</t>
+    <t>2025-03-25T14:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T14:07:20+00:00</t>
+    <t>2025-03-31T09:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T09:17:15+00:00</t>
+    <t>2025-04-14T15:21:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-14T15:21:44+00:00</t>
+    <t>2025-04-23T09:31:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1558,17 +1558,17 @@
   <dimension ref="A1:AM60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="57.6171875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="46.27734375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.0859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="49.39453125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="39.671875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="102.703125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="88.046875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1577,25 +1577,25 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="89.85546875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="38.27734375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="77.03515625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="32.81640625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="89.0078125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="45.6171875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="76.30859375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="39.109375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2149" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2495" uniqueCount="462">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T09:31:53+00:00</t>
+    <t>2025-04-24T14:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1040,6 +1040,196 @@
     <t>XPN</t>
   </si>
   <si>
+    <t>RelatedPerson.name.id</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name.extension</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name.extension:assemblyOrder</t>
+  </si>
+  <si>
+    <t>assemblyOrder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {humanname-assembly-order}
+</t>
+  </si>
+  <si>
+    <t>Preferred display order of name parts</t>
+  </si>
+  <si>
+    <t>A code that represents the preferred display order of the components of this human name.</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | nickname | anonymous | old | maiden</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this name.</t>
+  </si>
+  <si>
+    <t>Applications can assume that a name is current unless it explicitly says that it is temporary or old.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/name-use</t>
+  </si>
+  <si>
+    <t>HumanName.use</t>
+  </si>
+  <si>
+    <t>unique(./use)</t>
+  </si>
+  <si>
+    <t>XPN.7, but often indicated by which field contains the name</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name.text</t>
+  </si>
+  <si>
+    <t>Text representation of the full name</t>
+  </si>
+  <si>
+    <t>Specifies the entire name as it should be displayed e.g. on an application UI. This may be provided instead of or as well as the specific parts.</t>
+  </si>
+  <si>
+    <t>Can provide both a text representation and parts. Applications updating a name SHALL ensure that when both text and parts are present,  no content is included in the text that isn't found in a part.</t>
+  </si>
+  <si>
+    <t>A renderable, unencoded form.</t>
+  </si>
+  <si>
+    <t>HumanName.text</t>
+  </si>
+  <si>
+    <t>./formatted</t>
+  </si>
+  <si>
+    <t>implied by XPN.11</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name.family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">surname
+</t>
+  </si>
+  <si>
+    <t>Family name (often called 'Surname')</t>
+  </si>
+  <si>
+    <t>The part of a name that links to the genealogy. In some cultures (e.g. Eritrea) the family name of a son is the first name of his father.</t>
+  </si>
+  <si>
+    <t>Family Name may be decomposed into specific parts using extensions (de, nl, es related cultures).</t>
+  </si>
+  <si>
+    <t>HumanName.family</t>
+  </si>
+  <si>
+    <t>./part[partType = FAM]</t>
+  </si>
+  <si>
+    <t>XPN.1/FN.1</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name.given</t>
+  </si>
+  <si>
+    <t>first name
+middle name</t>
+  </si>
+  <si>
+    <t>Given names (not always 'first'). Includes middle names</t>
+  </si>
+  <si>
+    <t>Given name.</t>
+  </si>
+  <si>
+    <t>If only initials are recorded, they may be used in place of the full name parts. Initials may be separated into multiple given names but often aren't due to paractical limitations.  This element is not called "first name" since given names do not always come first.</t>
+  </si>
+  <si>
+    <t>HumanName.given</t>
+  </si>
+  <si>
+    <t>./part[partType = GIV]</t>
+  </si>
+  <si>
+    <t>XPN.2 + XPN.3</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name.prefix</t>
+  </si>
+  <si>
+    <t>Civilité</t>
+  </si>
+  <si>
+    <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the start of the name.</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J245-Civilite-CISIS/FHIR/JDV-J245-Civilite-CISIS</t>
+  </si>
+  <si>
+    <t>HumanName.prefix</t>
+  </si>
+  <si>
+    <t>./part[partType = PFX]</t>
+  </si>
+  <si>
+    <t>XPN.5</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name.suffix</t>
+  </si>
+  <si>
+    <t>Titre</t>
+  </si>
+  <si>
+    <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the end of the name.</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J246-Titre-CISIS/FHIR/JDV-J246-Titre-CISIS</t>
+  </si>
+  <si>
+    <t>HumanName.suffix</t>
+  </si>
+  <si>
+    <t>./part[partType = SFX]</t>
+  </si>
+  <si>
+    <t>XPN/4</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when name was/is in use</t>
+  </si>
+  <si>
+    <t>Indicates the period of time when this name was valid for the named person.</t>
+  </si>
+  <si>
+    <t>Allows names to be placed in historical context.</t>
+  </si>
+  <si>
+    <t>HumanName.period</t>
+  </si>
+  <si>
+    <t>./usablePeriod[type="IVL&lt;TS&gt;"]</t>
+  </si>
+  <si>
+    <t>XPN.13 + XPN.14</t>
+  </si>
+  <si>
     <t>RelatedPerson.telecom</t>
   </si>
   <si>
@@ -1157,10 +1347,6 @@
   </si>
   <si>
     <t>RelatedPerson.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
   </si>
   <si>
     <t>Period of time that this relationship is considered valid</t>
@@ -1555,12 +1741,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM60"/>
+  <dimension ref="A1:AM70"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.39453125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="39.671875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1595,7 +1781,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="76.30859375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="39.109375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="48.16015625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6960,7 +7146,7 @@
         <v>77</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>76</v>
@@ -6972,20 +7158,16 @@
         <v>76</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>333</v>
+        <v>99</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>334</v>
+        <v>100</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>337</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>76</v>
       </c>
@@ -7033,47 +7215,47 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>332</v>
+        <v>102</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>329</v>
+        <v>76</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>338</v>
+        <v>76</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>339</v>
+        <v>103</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>340</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>76</v>
@@ -7082,21 +7264,21 @@
         <v>76</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>165</v>
+        <v>106</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>342</v>
+        <v>107</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" t="s" s="2">
-        <v>344</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>76</v>
       </c>
@@ -7120,62 +7302,64 @@
         <v>76</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>309</v>
+        <v>76</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>345</v>
+        <v>76</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>346</v>
+        <v>76</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>341</v>
+        <v>113</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>347</v>
+        <v>103</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>348</v>
+        <v>76</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="C51" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>335</v>
+      </c>
       <c r="D51" t="s" s="2">
         <v>76</v>
       </c>
@@ -7193,16 +7377,16 @@
         <v>76</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>351</v>
+        <v>337</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7253,22 +7437,22 @@
         <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>349</v>
+        <v>113</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>353</v>
+        <v>76</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>76</v>
@@ -7279,10 +7463,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7293,31 +7477,31 @@
         <v>77</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>355</v>
+        <v>165</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>357</v>
+        <v>341</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>359</v>
+        <v>343</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>76</v>
@@ -7342,13 +7526,11 @@
         <v>76</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>76</v>
+        <v>344</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>76</v>
@@ -7366,36 +7548,36 @@
         <v>76</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>329</v>
+        <v>76</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>360</v>
+        <v>346</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>361</v>
+        <v>347</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7406,7 +7588,7 @@
         <v>77</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>76</v>
@@ -7415,20 +7597,22 @@
         <v>76</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>363</v>
+        <v>99</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>350</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>351</v>
+      </c>
       <c r="O53" t="s" s="2">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>76</v>
@@ -7477,13 +7661,13 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>76</v>
@@ -7492,29 +7676,29 @@
         <v>97</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>368</v>
+        <v>355</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>76</v>
+        <v>357</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>85</v>
@@ -7526,18 +7710,20 @@
         <v>76</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>370</v>
+        <v>99</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>76</v>
@@ -7586,7 +7772,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -7601,32 +7787,32 @@
         <v>97</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>374</v>
+        <v>76</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>76</v>
+        <v>363</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>76</v>
+        <v>365</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>76</v>
@@ -7635,23 +7821,21 @@
         <v>76</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>376</v>
+        <v>99</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>380</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>76</v>
       </c>
@@ -7699,7 +7883,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7714,21 +7898,21 @@
         <v>97</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>76</v>
+        <v>371</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7748,16 +7932,16 @@
         <v>76</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K56" t="s" s="2">
         <v>99</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>100</v>
+        <v>373</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>101</v>
+        <v>374</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7784,13 +7968,11 @@
         <v>76</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>76</v>
+        <v>375</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>76</v>
@@ -7808,47 +7990,47 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>102</v>
+        <v>376</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>103</v>
+        <v>377</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>76</v>
+        <v>378</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>76</v>
@@ -7857,20 +8039,18 @@
         <v>76</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>107</v>
+        <v>380</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>76</v>
@@ -7895,13 +8075,11 @@
         <v>76</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>76</v>
+        <v>382</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>76</v>
@@ -7919,7 +8097,7 @@
         <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>113</v>
+        <v>383</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -7931,59 +8109,57 @@
         <v>76</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>103</v>
+        <v>384</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>76</v>
+        <v>385</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>385</v>
+        <v>76</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="J58" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>106</v>
+        <v>387</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>195</v>
+        <v>390</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>76</v>
@@ -8032,36 +8208,36 @@
         <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>188</v>
+        <v>392</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>76</v>
+        <v>393</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8069,10 +8245,10 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>76</v>
@@ -8084,19 +8260,19 @@
         <v>76</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>222</v>
+        <v>395</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>76</v>
@@ -8121,13 +8297,13 @@
         <v>76</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>169</v>
+        <v>76</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>170</v>
+        <v>76</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>171</v>
+        <v>76</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>76</v>
@@ -8145,36 +8321,36 @@
         <v>76</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>76</v>
+        <v>329</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>97</v>
+        <v>400</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>76</v>
+        <v>402</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8194,22 +8370,20 @@
         <v>76</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>206</v>
+        <v>165</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>76</v>
@@ -8234,13 +8408,13 @@
         <v>76</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>76</v>
+        <v>309</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>76</v>
+        <v>407</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>76</v>
+        <v>408</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>76</v>
@@ -8258,7 +8432,7 @@
         <v>76</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -8273,12 +8447,1126 @@
         <v>97</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM60" t="s" s="2">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM70" t="s" s="2">
         <v>76</v>
       </c>
     </row>

--- a/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T14:52:25+00:00</t>
+    <t>2025-04-28T07:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:47:42+00:00</t>
+    <t>2025-04-28T07:48:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -8030,7 +8030,7 @@
         <v>77</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>76</v>

--- a/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:48:19+00:00</t>
+    <t>2025-04-28T09:06:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T09:06:14+00:00</t>
+    <t>2025-04-28T09:53:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T09:53:39+00:00</t>
+    <t>2025-05-06T15:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:44:46+00:00</t>
+    <t>2025-05-06T15:53:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:53:54+00:00</t>
+    <t>2025-05-06T15:58:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:58:22+00:00</t>
+    <t>2025-05-20T10:20:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-related-person-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T10:20:09+00:00</t>
+    <t>2025-05-20T12:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
